--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -25250,4 +25250,10 @@
   </sheetData>
   <autoFilter ref="A1:G28"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e962d134-526b-49fe-8fc7-dd80537250d0}" enabled="1" method="Standard" siteId="{eaa6be54-4687-40c4-9827-c044bd8e8d3c}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wmoomm-my.sharepoint.com/personal/zandreeva_wmo_int/Documents/Desktop/Claude/EW4ALL/RA-II-V/EW4All dashboard/export/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EDA2945AE9E768EA1C53196E10DA2291C3D9BE9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CF2D5E9-E0EE-4A47-82EA-6E634C86BA0B}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_EDA2945AE9E768EA1C53196E10DA2291C3D9BE9D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A0EE23-52FA-41F0-8D9F-B892B2A9AA65}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4782,7 +4782,7 @@
     <t>RADARSAT / RCM</t>
   </si>
   <si>
-    <t>Sulphur Dioxide Detection</t>
+    <t>Sulphur Dioxide Detection (SO2D)</t>
   </si>
 </sst>
 </file>
